--- a/banks/W05_Kahoot匯入.xlsx
+++ b/banks/W05_Kahoot匯入.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -491,19 +491,19 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
+          <t>配位基</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
           <t>結合位置</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>協同性</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>配位基</t>
-        </is>
-      </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
           <t>血基質</t>
@@ -514,7 +514,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -531,25 +531,25 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
+          <t>結合位置</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
           <t>異位調節</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>解離常數</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>結合位置</t>
-        </is>
-      </c>
       <c r="F3" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -566,14 +566,14 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>血紅素</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>肌紅素</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>血紅素</t>
-        </is>
-      </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
           <t>異位調節</t>
@@ -584,7 +584,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -596,14 +596,14 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
+          <t>解離常數</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
           <t>血紅素</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>解離常數</t>
-        </is>
-      </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
           <t>結合位置</t>
@@ -619,7 +619,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -741,25 +741,25 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>異位調節</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
           <t>肌動蛋白</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>解離常數</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>異位調節</t>
-        </is>
-      </c>
       <c r="F9" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -771,19 +771,19 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
+          <t>異位調節</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>肌凝蛋白</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>波耳效應</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>異位調節</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>肌凝蛋白</t>
-        </is>
-      </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
           <t>肌動蛋白</t>
@@ -794,7 +794,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -806,30 +806,30 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
+          <t>異位調節</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>肌動蛋白</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>氧合曲線</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
           <t>解離常數</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>異位調節</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>肌動蛋白</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>氧合曲線</t>
-        </is>
-      </c>
       <c r="F11" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -881,25 +881,25 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>氧合曲線</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>血基質</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>抗體</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>氧合曲線</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>血基質</t>
-        </is>
-      </c>
       <c r="F13" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -911,30 +911,30 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
+          <t>抗原</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
           <t>肌紅素</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>協同性</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>抗體</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>抗原</t>
-        </is>
-      </c>
       <c r="F14" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -946,30 +946,30 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
+          <t>肌紅素</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>結合位置</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>解離常數</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
           <t>肌動蛋白</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>肌紅素</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>結合位置</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>解離常數</t>
-        </is>
-      </c>
       <c r="F15" s="2" t="n">
         <v>30</v>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -1005,6 +1005,146 @@
       <c r="G16" s="2" t="inlineStr">
         <is>
           <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>(標圖:氧解離曲線圖) 標號1所在的曲線是哪一種蛋白質?</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>肌紅素</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>肌動蛋白</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>抗體</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>血紅素</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>(標圖:氧解離曲線圖) 標號2所在的曲線是哪一種蛋白質?</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>血紅素</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>肌紅素</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>抗原</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>肌凝蛋白</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>哪一個配對正確?</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>協同性—肌紅素只有一條胜肽鏈</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>鐮刀型貧血—鐵離子變成Fe³⁺</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>解離常數—血紅素的曲線呈S形</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>波耳效應—pH下降時血紅素放掉氧</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>為什麼一氧化碳中毒時人還是會缺氧?</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>CO佔住血基質的結合位置比O2抓得更緊</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>CO會把Fe²⁺變成Fe³⁺</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>CO會讓協同性消失</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>CO會讓紅血球全部死亡</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
         </is>
       </c>
     </row>
